--- a/assets/constructions/examples/ctd_inserts_drilling.xlsx
+++ b/assets/constructions/examples/ctd_inserts_drilling.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,11 +634,36 @@
           <t>adintws</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TCF040204APV34 WPK10CH</t>
+          <t>TCF120405ECV38 WU40PH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -648,19 +673,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>WID_TopCut_A-P</t>
+          <t>WID_TopCut_E-C</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -670,7 +695,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>V34</t>
+          <t>V38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -681,12 +706,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>TCF040204</t>
+          <t>TCF120405</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>WPK10CH</t>
+          <t>WU40PH</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -702,7 +727,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>TCF040204APV34</t>
+          <t>TCF120405ECV38</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -710,7 +735,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -724,13 +749,13 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>4.14</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="b">
@@ -741,7 +766,7 @@
         <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
@@ -754,7 +779,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>CVD</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -767,64 +792,83 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>WIDIA_TopCut_A-P</t>
+          <t>WIDIA_TopCut_E-C</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DS20-0407-P-M7W     4324</t>
+          <t>TCF180614HPV34 WU40PH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COR_DS20-0407-P</t>
+          <t>WID_TopCut_H-P</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>CoroDrill DS20-0407-P</t>
-        </is>
-      </c>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>V34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CoroDrillⓇ DS20 insert for drilling</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Top Cut 4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TCF180614</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>WU40PH</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="O3" t="b">
@@ -835,7 +879,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>DS20-0407</t>
+          <t>TCF180614HPV34</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -843,7 +887,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -853,29 +897,31 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>18.04</v>
+      </c>
       <c r="Y3" t="n">
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.289999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>11</v>
+      </c>
       <c r="AE3" t="n">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
@@ -885,12 +931,12 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>CVD</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
+          <t>2017 / WIDIA Master Catalog RU</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -898,19 +944,30 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>COR_DS20-0407-P</t>
+          <t>WIDIA_TopCut_H-P</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DS20-0205-P-L5W     4344</t>
+          <t>DS20-0205-P-L5W     2044</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -920,7 +977,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PMNS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -950,7 +1007,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1037,11 +1094,22 @@
           <t>WORKPIECE</t>
         </is>
       </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XOMT09T30636 TPC35</t>
+          <t>TCF070304CCV36 WU40PH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1051,19 +1119,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>PMK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>WID_XO09T3</t>
+          <t>WID_TopCut_C-C</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,23 +1141,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>V36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Top Cut Plus</t>
+          <t>Top Cut 4</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>XOMT09T306</t>
+          <t>TCF070304</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>TPC35</t>
+          <t>WU40PH</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1105,7 +1173,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>XOMT09T30636</t>
+          <t>TCF070304CCV36</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1113,7 +1181,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1126,15 +1194,25 @@
           <t>#</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>11</v>
+      </c>
       <c r="AE5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
@@ -1147,12 +1225,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>CVD</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2010 / Widia Обработка отверстий</t>
+          <t>2017 / WIDIA Master Catalog RU</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -1160,55 +1238,78 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>WIDIA_XO09T3H</t>
+          <t>WIDIA_TopCut_C-C</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WCMX 06T308 PH6930</t>
+          <t>TCF150406FCV36 WN10PH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PALB_WC06T3_H</t>
+          <t>WID_TopCut_F-C</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PALBIT</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>V36</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Top Cut 4</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>WCMX06T308</t>
+          <t>TCF150406</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PH6930</t>
+          <t>WN10PH</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1224,15 +1325,15 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>WCMX06T308</t>
+          <t>TCF150406FCV36</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>C</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1242,24 +1343,28 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>#</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>9.525</v>
+        <v>14.94</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="Z6" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>12.2</v>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="b">
         <v>0</v>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>11</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
@@ -1277,7 +1382,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2020/Palbit General Catalogue</t>
+          <t>2017 / WIDIA Master Catalog RU</t>
         </is>
       </c>
       <c r="AM6" t="n">
@@ -1285,12 +1390,23 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>PALB_WC06T3H</t>
+          <t>WIDIA_TopCut_F-C</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
